--- a/新点e交易相关材料/项目服务器规划/北科院服务器规划-企业监管.xlsx
+++ b/新点e交易相关材料/项目服务器规划/北科院服务器规划-企业监管.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>序号</t>
   </si>
@@ -108,7 +108,7 @@
     <t>企业监管</t>
   </si>
   <si>
-    <t>档案系统主应用，解析服务</t>
+    <t>监管平台</t>
   </si>
   <si>
     <t>centos7.9最小化安装</t>
@@ -117,34 +117,52 @@
     <t>虚拟机/实体机</t>
   </si>
   <si>
+    <t>标配非集群</t>
+  </si>
+  <si>
+    <t>应用服务器</t>
+  </si>
+  <si>
+    <t>分析型数据库（StarRocks）</t>
+  </si>
+  <si>
+    <t>8030、9030</t>
+  </si>
+  <si>
+    <t>数据库服务器</t>
+  </si>
+  <si>
+    <t>图数据库(cansssadra)</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>8080、8081</t>
-  </si>
-  <si>
-    <t>标配非集群</t>
-  </si>
-  <si>
-    <t>应用服务器</t>
-  </si>
-  <si>
-    <t>打包服务*2</t>
-  </si>
-  <si>
-    <t>8082、8083</t>
+    <t>9042、7000、7001、7199</t>
+  </si>
+  <si>
+    <t>检索数据库服务器（ES）</t>
+  </si>
+  <si>
+    <t>围串标分析</t>
+  </si>
+  <si>
+    <t>交易大数据运算分析</t>
   </si>
   <si>
     <t>测试环境</t>
   </si>
   <si>
-    <t>电子档案系统</t>
-  </si>
-  <si>
-    <t>档案系统主应用、解析服务、打包服务*2</t>
+    <t>监管平台、围串标分析、交易大数据运算分析</t>
   </si>
   <si>
     <t>8080、8081、8082、8083</t>
+  </si>
+  <si>
+    <t>分析型数据库（StarRocks）、图数据库(cansssadra)、检索数据库服务器（ES）</t>
+  </si>
+  <si>
+    <t>8030、9030、9042、7000、7001、7199、9200</t>
   </si>
 </sst>
 </file>
@@ -548,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -566,32 +584,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -721,7 +713,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -733,34 +725,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -845,7 +837,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,26 +853,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1407,8 +1396,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="3"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1"/>
   <cols>
     <col min="3" max="3" width="16.5225225225225" customWidth="1"/>
     <col min="4" max="4" width="14.972972972973" style="1" customWidth="1"/>
@@ -1462,123 +1451,300 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="24.85" spans="1:13">
+    <row r="2" ht="15" spans="1:13">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
+        <v>4</v>
+      </c>
+      <c r="H2" s="5">
         <v>8</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="5">
+        <v>300</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5">
+        <v>8080</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="7">
-        <v>300</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7" t="s">
+      <c r="M2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="3" ht="15" spans="1:13">
+    <row r="3" ht="24.85" spans="1:13">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5">
+        <v>500</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="7">
-        <v>8</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="7">
-        <v>300</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="4" ht="37.3" spans="1:13">
+    <row r="4" ht="24.85" spans="1:13">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="I4" s="5">
+        <v>500</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="L4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="24.85" spans="1:13">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G5" s="5">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="5">
+        <v>500</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5">
+        <v>9200</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="7">
+      <c r="M5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:13">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8</v>
+      </c>
+      <c r="I6" s="5">
         <v>300</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>21</v>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5">
+        <v>8080</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="24.85" spans="1:13">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="5">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="5">
+        <v>300</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5">
+        <v>9000</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="37.3" spans="1:13">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="5">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5">
+        <v>300</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="74.55" spans="1:13">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="5">
+        <v>8</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="5">
+        <v>300</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="C8:C9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
